--- a/assets/constructions/examples/ctd_mhcr.xlsx
+++ b/assets/constructions/examples/ctd_mhcr.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO6"/>
+  <dimension ref="A1:AT6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -634,11 +634,36 @@
           <t>dcsfms</t>
         </is>
       </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A316-16SM440-06204K 1030</t>
+          <t>316-10SM545-10004K  1030</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -658,32 +683,32 @@
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>15.875</v>
+        <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>15.075</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H2" t="n">
         <v>0.4</v>
       </c>
       <c r="I2" t="n">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
       <c r="J2" t="n">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
       <c r="K2" t="b">
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
       <c r="M2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>INCH_EH:16</t>
+          <t>METRIC_EH:10</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -722,23 +747,23 @@
       </c>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="n">
-        <v>15.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Y2" t="n">
-        <v>18.7</v>
+        <v>12.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>15.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AA2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>10.5</v>
+        <v>-9</v>
       </c>
       <c r="AD2" t="n">
-        <v>13.5</v>
+        <v>2</v>
       </c>
       <c r="AE2" t="n">
         <v>0</v>
@@ -747,7 +772,7 @@
         <v>80000</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.062</v>
+        <v>0.025</v>
       </c>
       <c r="AH2" t="n">
         <v>0</v>
@@ -771,54 +796,71 @@
       <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>PMKS</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MM ERA160B10R0.2-3T10 IC08</t>
+          <t>4U402501DL25 WS15PE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ISCAR</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MM ERA</t>
+          <t>4U40</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
+          <t>PMS</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>KH</t>
+        </is>
+      </c>
       <c r="F3" t="n">
-        <v>16</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
+        <v>25</v>
+      </c>
+      <c r="G3" t="n">
+        <v>23.5</v>
+      </c>
       <c r="H3" t="n">
-        <v>0.2</v>
+        <v>0.75</v>
       </c>
       <c r="I3" t="n">
-        <v>10</v>
+        <v>37.5</v>
       </c>
       <c r="J3" t="n">
-        <v>10</v>
+        <v>37.5</v>
       </c>
       <c r="K3" t="b">
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>10</v>
+        <v>37.5</v>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>ISCAR_MM:T10</t>
+          <t>DUOLOCK:DL25</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -829,16 +871,20 @@
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>IC08</t>
+          <t>WS15PE</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr"/>
+          <t>AlTiN</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>DUO-LOCK</t>
+        </is>
+      </c>
       <c r="U3" t="n">
         <v>0</v>
       </c>
@@ -847,16 +893,20 @@
       </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>15.3</v>
+        <v>24</v>
       </c>
       <c r="Y3" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="Z3" t="inlineStr"/>
+        <v>57</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>24</v>
+      </c>
       <c r="AA3" t="n">
         <v>45</v>
       </c>
-      <c r="AB3" t="inlineStr"/>
+      <c r="AB3" t="n">
+        <v>21</v>
+      </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr"/>
@@ -867,7 +917,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2013/Multi_Master_Catalog.pdf</t>
+          <t>2018/Достижения</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -879,16 +929,35 @@
         <v>0</v>
       </c>
       <c r="AL3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>ZDL25</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>e8</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>PMKSH</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>316-16SM645-16004K  1030</t>
+          <t>A316-20SM645-07504K 1030</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -908,32 +977,32 @@
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>16</v>
+        <v>19.05</v>
       </c>
       <c r="G4" t="n">
-        <v>15.2</v>
+        <v>18.25</v>
       </c>
       <c r="H4" t="n">
         <v>0.4</v>
       </c>
       <c r="I4" t="n">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="J4" t="n">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="K4" t="b">
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="M4" t="n">
         <v>6</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>METRIC_EH:16</t>
+          <t>INCH_EH:20</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -972,13 +1041,13 @@
       </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>18.7</v>
+        <v>21.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AA4" t="n">
         <v>45</v>
@@ -997,7 +1066,7 @@
         <v>80000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.067</v>
+        <v>0.121</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
@@ -1021,11 +1090,22 @@
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>PMKS</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MM ERA100B06R0.2-3T06 IC08</t>
+          <t>MM ERA120B08R0.2-3T08 IC08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1045,30 +1125,30 @@
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K5" t="b">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M5" t="n">
         <v>3</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>ISCAR_MM:T06</t>
+          <t>ISCAR_MM:T08</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1097,10 +1177,10 @@
       </c>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>9.6</v>
+        <v>11.7</v>
       </c>
       <c r="Y5" t="n">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
@@ -1134,54 +1214,71 @@
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MM ERA200B12R0.2-3T12 IC08</t>
+          <t>4U401201DL12 WS15PE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ISCAR</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MM ERA</t>
+          <t>4U40</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+          <t>PMS</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>KH</t>
+        </is>
+      </c>
       <c r="F6" t="n">
-        <v>20</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="G6" t="n">
+        <v>10.5</v>
+      </c>
       <c r="H6" t="n">
-        <v>0.2</v>
+        <v>0.75</v>
       </c>
       <c r="I6" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J6" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="K6" t="b">
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>ISCAR_MM:T12</t>
+          <t>DUOLOCK:DL12</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1192,16 +1289,20 @@
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>IC08</t>
+          <t>WS15PE</t>
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr"/>
+          <t>AlTiN</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>DUO-LOCK</t>
+        </is>
+      </c>
       <c r="U6" t="n">
         <v>0</v>
       </c>
@@ -1210,16 +1311,20 @@
       </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="n">
-        <v>18.45</v>
+        <v>11.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="Z6" t="inlineStr"/>
+        <v>27</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>11.5</v>
+      </c>
       <c r="AA6" t="n">
         <v>45</v>
       </c>
-      <c r="AB6" t="inlineStr"/>
+      <c r="AB6" t="n">
+        <v>9.5</v>
+      </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
@@ -1230,7 +1335,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2013/Multi_Master_Catalog.pdf</t>
+          <t>2018/Достижения</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1242,11 +1347,30 @@
         <v>0</v>
       </c>
       <c r="AL6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>ZDL12</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>e8</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>PMKSH</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
